--- a/AAII_Financials/Quarterly/GEVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEVI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
   <si>
     <t>GEVI</t>
   </si>
@@ -656,100 +656,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40268</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40178</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40086</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>200</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
@@ -771,23 +775,26 @@
       <c r="M8" s="3">
         <v>0</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3">
         <v>1500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -803,17 +810,17 @@
       <c r="G9" s="3">
         <v>0</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
+      <c r="K9" s="3">
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
@@ -824,46 +831,49 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3">
         <v>1300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>200</v>
       </c>
       <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
+      <c r="K10" s="3">
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
@@ -874,20 +884,23 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3">
         <v>200</v>
       </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
       <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
         <v>200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,8 +919,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -956,8 +970,11 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,8 +1023,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1017,17 +1037,17 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1036,33 +1056,36 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
         <v>1800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1079,11 +1102,11 @@
       <c r="I15" s="3">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1106,8 +1129,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,35 +1149,36 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>400</v>
+        <v>9200</v>
       </c>
       <c r="E17" s="3">
         <v>400</v>
       </c>
       <c r="F17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G17" s="3">
         <v>300</v>
       </c>
       <c r="H17" s="3">
+        <v>300</v>
+      </c>
+      <c r="I17" s="3">
         <v>2400</v>
       </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
       <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
         <v>100</v>
       </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
       <c r="L17" s="3">
         <v>0</v>
       </c>
@@ -1159,30 +1186,33 @@
         <v>0</v>
       </c>
       <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
         <v>100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-9000</v>
       </c>
       <c r="E18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="F18" s="3">
         <v>-300</v>
@@ -1191,40 +1221,43 @@
         <v>-300</v>
       </c>
       <c r="H18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-2400</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
       <c r="L18" s="3">
         <v>0</v>
       </c>
       <c r="M18" s="3">
         <v>0</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3">
         <v>-4200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,13 +1276,14 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1278,73 +1312,79 @@
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>1700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-9000</v>
       </c>
       <c r="E21" s="3">
         <v>-400</v>
       </c>
       <c r="F21" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="G21" s="3">
         <v>-300</v>
       </c>
       <c r="H21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-2300</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
         <v>0</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M21" s="3">
         <v>0</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-2100</v>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P21" s="3">
         <v>-2100</v>
       </c>
       <c r="Q21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="R21" s="3">
         <v>-1400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1378,44 +1418,47 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3">
         <v>900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-400</v>
+        <v>-9000</v>
       </c>
       <c r="E23" s="3">
         <v>-400</v>
       </c>
       <c r="F23" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="G23" s="3">
         <v>-300</v>
       </c>
       <c r="H23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2300</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
         <v>0</v>
       </c>
@@ -1429,22 +1472,25 @@
         <v>0</v>
       </c>
       <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1478,23 +1524,26 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,29 +1592,32 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-400</v>
+        <v>-9000</v>
       </c>
       <c r="E26" s="3">
         <v>-400</v>
       </c>
       <c r="F26" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="G26" s="3">
         <v>-300</v>
       </c>
       <c r="H26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2300</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
         <v>0</v>
       </c>
@@ -1579,43 +1631,46 @@
         <v>0</v>
       </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-400</v>
+        <v>-9000</v>
       </c>
       <c r="E27" s="3">
         <v>-400</v>
       </c>
       <c r="F27" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="G27" s="3">
         <v>-300</v>
       </c>
       <c r="H27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2300</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
         <v>0</v>
       </c>
@@ -1629,22 +1684,25 @@
         <v>0</v>
       </c>
       <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1751,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1717,34 +1778,37 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-100</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-100</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O29" s="3">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3">
         <v>8300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1857,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,13 +1910,16 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1878,73 +1948,79 @@
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-400</v>
+        <v>-9000</v>
       </c>
       <c r="E33" s="3">
         <v>-400</v>
       </c>
       <c r="F33" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="G33" s="3">
         <v>-300</v>
       </c>
       <c r="H33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I33" s="3">
         <v>-2300</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
       <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2069,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-400</v>
+        <v>-9000</v>
       </c>
       <c r="E35" s="3">
         <v>-400</v>
       </c>
       <c r="F35" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="G35" s="3">
         <v>-300</v>
       </c>
       <c r="H35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I35" s="3">
         <v>-2300</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
       <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40268</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40178</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40086</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2203,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,13 +2224,14 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="E41" s="3">
         <v>100</v>
@@ -2159,7 +2246,7 @@
         <v>100</v>
       </c>
       <c r="I41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
@@ -2173,8 +2260,8 @@
       <c r="M41" s="3">
         <v>0</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
+      <c r="N41" s="3">
+        <v>0</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>4</v>
@@ -2188,8 +2275,11 @@
       <c r="R41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2238,31 +2328,34 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2288,13 +2381,16 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E44" s="3">
         <v>100</v>
@@ -2308,8 +2404,8 @@
       <c r="H44" s="3">
         <v>100</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
+      <c r="I44" s="3">
+        <v>100</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
@@ -2323,8 +2419,8 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2338,8 +2434,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2352,8 +2451,8 @@
       <c r="F45" s="3">
         <v>0</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
+      <c r="G45" s="3">
+        <v>0</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
@@ -2364,8 +2463,8 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -2388,13 +2487,16 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="E46" s="3">
         <v>200</v>
@@ -2409,7 +2511,7 @@
         <v>200</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J46" s="3">
         <v>0</v>
@@ -2423,8 +2525,8 @@
       <c r="M46" s="3">
         <v>0</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
+      <c r="N46" s="3">
+        <v>0</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>4</v>
@@ -2438,8 +2540,11 @@
       <c r="R46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2488,13 +2593,16 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E48" s="3">
         <v>0</v>
@@ -2503,19 +2611,19 @@
         <v>0</v>
       </c>
       <c r="G48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
         <v>100</v>
       </c>
       <c r="I48" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>300</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
+      <c r="K48" s="3">
+        <v>300</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
@@ -2532,14 +2640,17 @@
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2558,8 +2669,8 @@
       <c r="H49" s="3">
         <v>4200</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
+      <c r="I49" s="3">
+        <v>4200</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>4</v>
@@ -2576,8 +2687,8 @@
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -2588,8 +2699,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2752,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,8 +2805,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2699,8 +2819,8 @@
       <c r="E52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -2714,8 +2834,8 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
@@ -2732,14 +2852,17 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,13 +2911,16 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4400</v>
+        <v>5300</v>
       </c>
       <c r="E54" s="3">
         <v>4400</v>
@@ -2806,16 +2932,16 @@
         <v>4400</v>
       </c>
       <c r="H54" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I54" s="3">
         <v>4500</v>
-      </c>
-      <c r="I54" s="3">
-        <v>300</v>
       </c>
       <c r="J54" s="3">
         <v>300</v>
       </c>
       <c r="K54" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
@@ -2823,8 +2949,8 @@
       <c r="M54" s="3">
         <v>0</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
+      <c r="N54" s="3">
+        <v>0</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>4</v>
@@ -2838,8 +2964,11 @@
       <c r="R54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2987,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,22 +3008,23 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H57" s="3">
         <v>0</v>
@@ -2910,8 +3041,8 @@
       <c r="L57" s="3">
         <v>0</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
+      <c r="M57" s="3">
+        <v>0</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
@@ -2928,25 +3059,28 @@
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>200</v>
+      </c>
+      <c r="E58" s="3">
         <v>100</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
+      <c r="H58" s="3">
+        <v>0</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>4</v>
@@ -2954,14 +3088,14 @@
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K58" s="3">
-        <v>100</v>
+      <c r="K58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
+      <c r="M58" s="3">
+        <v>100</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
@@ -2978,34 +3112,37 @@
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>400</v>
       </c>
       <c r="J59" s="3">
         <v>400</v>
       </c>
       <c r="K59" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -3013,8 +3150,8 @@
       <c r="M59" s="3">
         <v>0</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
+      <c r="N59" s="3">
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
@@ -3028,43 +3165,46 @@
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>500</v>
-      </c>
-      <c r="I60" s="3">
-        <v>400</v>
       </c>
       <c r="J60" s="3">
         <v>400</v>
       </c>
       <c r="K60" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L60" s="3">
         <v>100</v>
       </c>
       <c r="M60" s="3">
-        <v>0</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="N60" s="3">
+        <v>0</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>4</v>
@@ -3078,8 +3218,11 @@
       <c r="R60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3128,13 +3271,16 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
+      <c r="D62" s="3">
+        <v>100</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>4</v>
@@ -3145,12 +3291,12 @@
       <c r="G62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3163,8 +3309,8 @@
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -3178,8 +3324,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3377,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3430,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,43 +3483,46 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>600</v>
-      </c>
-      <c r="I66" s="3">
-        <v>400</v>
       </c>
       <c r="J66" s="3">
         <v>400</v>
       </c>
       <c r="K66" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L66" s="3">
         <v>100</v>
       </c>
       <c r="M66" s="3">
-        <v>0</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="N66" s="3">
+        <v>0</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>4</v>
@@ -3378,8 +3536,11 @@
       <c r="R66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3559,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3610,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3663,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3716,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,28 +3769,31 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-69100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-60100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-59700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-59400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-59100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-58800</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-56500</v>
       </c>
       <c r="J72" s="3">
         <v>-56500</v>
@@ -3628,13 +3802,13 @@
         <v>-56500</v>
       </c>
       <c r="L72" s="3">
-        <v>-56400</v>
+        <v>-56500</v>
       </c>
       <c r="M72" s="3">
         <v>-56400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
+      <c r="N72" s="3">
+        <v>-56400</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
@@ -3648,8 +3822,11 @@
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3875,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3928,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,28 +3981,31 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E76" s="3">
         <v>3000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-100</v>
       </c>
       <c r="J76" s="3">
         <v>-100</v>
@@ -3831,10 +4017,10 @@
         <v>-100</v>
       </c>
       <c r="M76" s="3">
-        <v>0</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="N76" s="3">
+        <v>0</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>4</v>
@@ -3848,8 +4034,11 @@
       <c r="R76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4087,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40268</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40178</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40086</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-400</v>
+        <v>-9000</v>
       </c>
       <c r="E81" s="3">
         <v>-400</v>
       </c>
       <c r="F81" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="G81" s="3">
         <v>-300</v>
       </c>
       <c r="H81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I81" s="3">
         <v>-2300</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
       <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4221,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4049,8 +4248,8 @@
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>4</v>
@@ -4067,14 +4266,17 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4325,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4378,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4431,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4484,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,13 +4537,16 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="E89" s="3">
         <v>-200</v>
@@ -4341,11 +4558,11 @@
         <v>-200</v>
       </c>
       <c r="H89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
         <v>0</v>
       </c>
@@ -4361,8 +4578,8 @@
       <c r="N89" s="3">
         <v>0</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
+      <c r="O89" s="3">
+        <v>0</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>4</v>
@@ -4373,8 +4590,11 @@
       <c r="R89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,8 +4613,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4425,11 +4646,11 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -4443,8 +4664,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4717,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,37 +4770,40 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>0</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
@@ -4587,14 +4817,17 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +4846,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4663,8 +4897,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4950,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5003,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,16 +5056,19 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>900</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
-      </c>
-      <c r="E100" s="3">
-        <v>200</v>
       </c>
       <c r="F100" s="3">
         <v>200</v>
@@ -4831,19 +5077,19 @@
         <v>200</v>
       </c>
       <c r="H100" s="3">
+        <v>200</v>
+      </c>
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>4</v>
@@ -4863,8 +5109,11 @@
       <c r="R100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4913,13 +5162,16 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
@@ -4931,11 +5183,11 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
@@ -4951,8 +5203,8 @@
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>4</v>
@@ -4961,6 +5213,9 @@
         <v>4</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GEVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
   <si>
     <t>GEVI</t>
   </si>
@@ -656,110 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>40268</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>40178</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>40086</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
@@ -778,31 +785,37 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
+      <c r="O8" s="3">
+        <v>0</v>
       </c>
       <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3">
         <v>1500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -813,20 +826,20 @@
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
+      <c r="I9" s="3">
+        <v>0</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
+      <c r="K9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
@@ -834,52 +847,58 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3">
         <v>1300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>3800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
       <c r="F10" s="3">
+        <v>200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
+      <c r="I10" s="3">
+        <v>0</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
+      <c r="K10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
@@ -887,20 +906,26 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P10" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>0</v>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R10" s="3">
         <v>200</v>
       </c>
       <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
+        <v>200</v>
+      </c>
+      <c r="U10" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,8 +945,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -973,8 +1000,14 @@
       <c r="S12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1026,13 +1059,19 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>900</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1040,58 +1079,64 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
         <v>1800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>4000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>1900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
+      <c r="E15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
@@ -1105,14 +1150,14 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>4</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1132,8 +1177,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,114 +1201,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>600</v>
+      </c>
+      <c r="F17" s="3">
         <v>9200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2400</v>
       </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
         <v>100</v>
       </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
       <c r="N17" s="3">
         <v>0</v>
       </c>
       <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
         <v>100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>6100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>8000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-9000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-300</v>
       </c>
       <c r="H18" s="3">
         <v>-300</v>
       </c>
       <c r="I18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2400</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
       <c r="N18" s="3">
         <v>0</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
+      <c r="O18" s="3">
+        <v>0</v>
       </c>
       <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-5200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-4000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,8 +1342,10 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1315,76 +1382,88 @@
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>1700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>2900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>2800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-9000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2300</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
+      <c r="L21" s="3">
+        <v>0</v>
       </c>
       <c r="M21" s="3">
         <v>0</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0</v>
       </c>
       <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-2100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1421,50 +1500,56 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>5300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>1800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-9000</v>
+        <v>-3500</v>
       </c>
       <c r="E23" s="3">
         <v>-400</v>
       </c>
       <c r="F23" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="G23" s="3">
         <v>-400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2300</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
       <c r="L23" s="3">
         <v>0</v>
       </c>
@@ -1475,22 +1560,28 @@
         <v>0</v>
       </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-7600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-3100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1527,23 +1618,29 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>4</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,35 +1692,41 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-9000</v>
+        <v>-3500</v>
       </c>
       <c r="E26" s="3">
         <v>-400</v>
       </c>
       <c r="F26" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="G26" s="3">
         <v>-400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2300</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
       <c r="L26" s="3">
         <v>0</v>
       </c>
@@ -1634,49 +1737,55 @@
         <v>0</v>
       </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-7600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-3100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-9000</v>
+        <v>-3500</v>
       </c>
       <c r="E27" s="3">
         <v>-400</v>
       </c>
       <c r="F27" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="G27" s="3">
         <v>-400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
       <c r="L27" s="3">
         <v>0</v>
       </c>
@@ -1687,22 +1796,28 @@
         <v>0</v>
       </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-7600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-3100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,13 +1869,19 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -1781,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1792,23 +1913,29 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>4</v>
+      <c r="O29" s="3">
+        <v>-100</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3">
         <v>8300</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-7400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1987,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,8 +2046,14 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1951,49 +2090,55 @@
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-2900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-2800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-9000</v>
+        <v>-3500</v>
       </c>
       <c r="E33" s="3">
         <v>-400</v>
       </c>
       <c r="F33" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="G33" s="3">
         <v>-400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-100</v>
       </c>
       <c r="L33" s="3">
         <v>0</v>
@@ -2008,19 +2153,25 @@
         <v>-100</v>
       </c>
       <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R33" s="3">
         <v>4500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-15000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-3200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,34 +2223,40 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-9000</v>
+        <v>-3500</v>
       </c>
       <c r="E35" s="3">
         <v>-400</v>
       </c>
       <c r="F35" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="G35" s="3">
         <v>-400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-100</v>
       </c>
       <c r="L35" s="3">
         <v>0</v>
@@ -2114,77 +2271,89 @@
         <v>-100</v>
       </c>
       <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R35" s="3">
         <v>4500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-15000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-3200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>40268</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>40178</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>40086</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2373,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,19 +2396,21 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>500</v>
+      </c>
+      <c r="F41" s="3">
         <v>600</v>
-      </c>
-      <c r="E41" s="3">
-        <v>100</v>
-      </c>
-      <c r="F41" s="3">
-        <v>100</v>
       </c>
       <c r="G41" s="3">
         <v>100</v>
@@ -2249,10 +2422,10 @@
         <v>100</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -2263,11 +2436,11 @@
       <c r="N41" s="3">
         <v>0</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
+      <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3">
+        <v>0</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>4</v>
@@ -2278,8 +2451,14 @@
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2331,20 +2510,26 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2357,11 +2542,11 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2384,8 +2569,14 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2393,10 +2584,10 @@
         <v>200</v>
       </c>
       <c r="E44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G44" s="3">
         <v>100</v>
@@ -2407,11 +2598,11 @@
       <c r="I44" s="3">
         <v>100</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
+      <c r="J44" s="3">
+        <v>100</v>
+      </c>
+      <c r="K44" s="3">
+        <v>100</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
@@ -2422,11 +2613,11 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2437,8 +2628,14 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2454,11 +2651,11 @@
       <c r="G45" s="3">
         <v>0</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
@@ -2466,11 +2663,11 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -2490,19 +2687,25 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F46" s="3">
         <v>900</v>
-      </c>
-      <c r="E46" s="3">
-        <v>200</v>
-      </c>
-      <c r="F46" s="3">
-        <v>200</v>
       </c>
       <c r="G46" s="3">
         <v>200</v>
@@ -2514,10 +2717,10 @@
         <v>200</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -2528,11 +2731,11 @@
       <c r="N46" s="3">
         <v>0</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>4</v>
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3">
+        <v>0</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>4</v>
@@ -2543,8 +2746,14 @@
       <c r="S46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2596,41 +2805,47 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>100</v>
+      </c>
+      <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
       <c r="G48" s="3">
         <v>0</v>
       </c>
       <c r="H48" s="3">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
         <v>100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2643,22 +2858,28 @@
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4200</v>
+        <v>3900</v>
       </c>
       <c r="E49" s="3">
-        <v>4200</v>
+        <v>3900</v>
       </c>
       <c r="F49" s="3">
         <v>4200</v>
@@ -2672,11 +2893,11 @@
       <c r="I49" s="3">
         <v>4200</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
+      <c r="J49" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K49" s="3">
+        <v>4200</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>4</v>
@@ -2690,11 +2911,11 @@
       <c r="O49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -2702,8 +2923,14 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2982,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,8 +3041,14 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2822,11 +3061,11 @@
       <c r="F52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -2837,11 +3076,11 @@
       <c r="K52" s="3">
         <v>0</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
@@ -2855,14 +3094,20 @@
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,8 +3159,14 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2923,10 +3174,10 @@
         <v>5300</v>
       </c>
       <c r="E54" s="3">
-        <v>4400</v>
+        <v>5300</v>
       </c>
       <c r="F54" s="3">
-        <v>4400</v>
+        <v>5300</v>
       </c>
       <c r="G54" s="3">
         <v>4400</v>
@@ -2935,28 +3186,28 @@
         <v>4400</v>
       </c>
       <c r="I54" s="3">
+        <v>4400</v>
+      </c>
+      <c r="J54" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K54" s="3">
         <v>4500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>300</v>
       </c>
-      <c r="L54" s="3">
-        <v>0</v>
-      </c>
-      <c r="M54" s="3">
-        <v>0</v>
-      </c>
       <c r="N54" s="3">
         <v>0</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>4</v>
+      <c r="O54" s="3">
+        <v>0</v>
+      </c>
+      <c r="P54" s="3">
+        <v>0</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>4</v>
@@ -2967,8 +3218,14 @@
       <c r="S54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3245,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,8 +3268,10 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3018,19 +3279,19 @@
         <v>100</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
       </c>
       <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
@@ -3044,11 +3305,11 @@
       <c r="M57" s="3">
         <v>0</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
+        <v>0</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
@@ -3062,47 +3323,53 @@
       <c r="S57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
+        <v>200</v>
+      </c>
+      <c r="G58" s="3">
         <v>100</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3115,49 +3382,55 @@
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="E59" s="3">
         <v>1400</v>
       </c>
       <c r="F59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
       <c r="N59" s="3">
         <v>0</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>4</v>
@@ -3168,49 +3441,55 @@
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F60" s="3">
         <v>1700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>4</v>
+      <c r="P60" s="3">
+        <v>0</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>4</v>
@@ -3221,8 +3500,14 @@
       <c r="S60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3274,19 +3559,25 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>100</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
+      <c r="F62" s="3">
+        <v>100</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>4</v>
@@ -3294,15 +3585,15 @@
       <c r="H62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3312,11 +3603,11 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -3327,8 +3618,14 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3677,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3736,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,49 +3795,55 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F66" s="3">
         <v>1800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>100</v>
       </c>
-      <c r="N66" s="3">
-        <v>0</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>4</v>
+      <c r="P66" s="3">
+        <v>0</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>4</v>
@@ -3539,8 +3854,14 @@
       <c r="S66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3881,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3936,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,8 +3995,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3719,8 +4054,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,50 +4113,56 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-69500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-69100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-60100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-59700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-59400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-59100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-58800</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-56500</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-56500</v>
       </c>
       <c r="L72" s="3">
         <v>-56500</v>
       </c>
       <c r="M72" s="3">
+        <v>-56500</v>
+      </c>
+      <c r="N72" s="3">
+        <v>-56500</v>
+      </c>
+      <c r="O72" s="3">
         <v>-56400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-56400</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3825,8 +4172,14 @@
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4231,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4290,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,34 +4349,40 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F76" s="3">
         <v>3500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3900</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K76" s="3">
-        <v>-100</v>
       </c>
       <c r="L76" s="3">
         <v>-100</v>
@@ -4020,13 +4391,13 @@
         <v>-100</v>
       </c>
       <c r="N76" s="3">
-        <v>0</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="O76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P76" s="3">
+        <v>0</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>4</v>
@@ -4037,8 +4408,14 @@
       <c r="S76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,92 +4467,104 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>40268</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>40178</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>40086</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-9000</v>
+        <v>-3500</v>
       </c>
       <c r="E81" s="3">
         <v>-400</v>
       </c>
       <c r="F81" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="G81" s="3">
         <v>-400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-100</v>
       </c>
       <c r="L81" s="3">
         <v>0</v>
@@ -4190,19 +4579,25 @@
         <v>-100</v>
       </c>
       <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R81" s="3">
         <v>4500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-15000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-3200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,16 +4617,18 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -4251,11 +4648,11 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>4</v>
@@ -4269,14 +4666,20 @@
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4731,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4790,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4849,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4908,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,19 +4967,25 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
-        <v>-200</v>
-      </c>
       <c r="F89" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="G89" s="3">
         <v>-200</v>
@@ -4561,14 +4994,14 @@
         <v>-200</v>
       </c>
       <c r="I89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
@@ -4581,11 +5014,11 @@
       <c r="O89" s="3">
         <v>0</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>4</v>
@@ -4593,8 +5026,14 @@
       <c r="S89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,8 +5053,10 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4649,14 +5090,14 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -4667,8 +5108,14 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +5167,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,43 +5226,49 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
@@ -4820,14 +5279,20 @@
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,8 +5312,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4900,8 +5367,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5426,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5485,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,43 +5544,49 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>400</v>
+      </c>
+      <c r="F100" s="3">
         <v>900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
-      </c>
-      <c r="F100" s="3">
-        <v>200</v>
-      </c>
-      <c r="G100" s="3">
-        <v>200</v>
       </c>
       <c r="H100" s="3">
         <v>200</v>
       </c>
       <c r="I100" s="3">
+        <v>200</v>
+      </c>
+      <c r="J100" s="3">
+        <v>200</v>
+      </c>
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>4</v>
@@ -5112,8 +5603,14 @@
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5165,20 +5662,26 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>500</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
@@ -5186,14 +5689,14 @@
         <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
@@ -5206,16 +5709,22 @@
       <c r="O102" s="3">
         <v>0</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>4</v>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GEVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
   <si>
     <t>GEVI</t>
   </si>
@@ -656,120 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>40268</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>40178</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>40086</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
@@ -791,23 +795,26 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3">
         <v>1500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -818,7 +825,7 @@
         <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -832,17 +839,17 @@
       <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="3">
-        <v>0</v>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M9" s="3">
         <v>0</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>4</v>
+      <c r="N9" s="3">
+        <v>0</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>4</v>
@@ -853,55 +860,58 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3">
         <v>1300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
         <v>300</v>
-      </c>
-      <c r="E10" s="3">
-        <v>200</v>
       </c>
       <c r="F10" s="3">
         <v>200</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
       <c r="J10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="3">
-        <v>0</v>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>4</v>
+      <c r="N10" s="3">
+        <v>0</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>4</v>
@@ -912,20 +922,23 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3">
         <v>200</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
       <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
         <v>200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,8 +960,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,17 +1082,20 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>900</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1085,17 +1105,17 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1104,33 +1124,36 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3">
         <v>1800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>4000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>4</v>
+      <c r="D15" s="3">
+        <v>100</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>4</v>
@@ -1138,14 +1161,14 @@
       <c r="F15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
+      <c r="G15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1156,11 +1179,11 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,44 +1229,45 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E17" s="3">
         <v>4000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>400</v>
       </c>
       <c r="H17" s="3">
         <v>400</v>
       </c>
       <c r="I17" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="J17" s="3">
         <v>300</v>
       </c>
       <c r="K17" s="3">
+        <v>300</v>
+      </c>
+      <c r="L17" s="3">
         <v>2400</v>
       </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
       <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
         <v>100</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
       <c r="O17" s="3">
         <v>0</v>
       </c>
@@ -1248,81 +1275,87 @@
         <v>0</v>
       </c>
       <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3">
         <v>100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
-        <v>-300</v>
-      </c>
       <c r="I18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J18" s="3">
         <v>-300</v>
       </c>
       <c r="K18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L18" s="3">
         <v>-2400</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
       <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
       <c r="O18" s="3">
         <v>0</v>
       </c>
       <c r="P18" s="3">
         <v>0</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3">
         <v>-4200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,8 +1377,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1388,82 +1422,88 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3">
         <v>1700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-400</v>
       </c>
       <c r="H21" s="3">
         <v>-400</v>
       </c>
       <c r="I21" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J21" s="3">
         <v>-300</v>
       </c>
       <c r="K21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L21" s="3">
         <v>-2300</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
       <c r="M21" s="3">
         <v>0</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O21" s="3">
-        <v>0</v>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P21" s="3">
         <v>0</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-2100</v>
+      <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S21" s="3">
         <v>-2100</v>
       </c>
       <c r="T21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="U21" s="3">
         <v>-1400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1506,53 +1546,56 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3">
         <v>900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-400</v>
       </c>
       <c r="H23" s="3">
         <v>-400</v>
       </c>
       <c r="I23" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J23" s="3">
         <v>-300</v>
       </c>
       <c r="K23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L23" s="3">
         <v>-2300</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
       <c r="M23" s="3">
         <v>0</v>
       </c>
@@ -1566,22 +1609,25 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1624,23 +1670,26 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,38 +1747,41 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-400</v>
       </c>
       <c r="H26" s="3">
         <v>-400</v>
       </c>
       <c r="I26" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J26" s="3">
         <v>-300</v>
       </c>
       <c r="K26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
       <c r="M26" s="3">
         <v>0</v>
       </c>
@@ -1743,52 +1795,55 @@
         <v>0</v>
       </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-400</v>
       </c>
       <c r="H27" s="3">
         <v>-400</v>
       </c>
       <c r="I27" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J27" s="3">
         <v>-300</v>
       </c>
       <c r="K27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
       <c r="M27" s="3">
         <v>0</v>
       </c>
@@ -1802,22 +1857,25 @@
         <v>0</v>
       </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,16 +1933,19 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1908,34 +1969,37 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-100</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-100</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3">
         <v>8300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-7400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,8 +2119,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2096,82 +2166,88 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3">
         <v>-1700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-400</v>
       </c>
       <c r="H33" s="3">
         <v>-400</v>
       </c>
       <c r="I33" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J33" s="3">
         <v>-300</v>
       </c>
       <c r="K33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
       <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>-100</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-15000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-400</v>
       </c>
       <c r="H35" s="3">
         <v>-400</v>
       </c>
       <c r="I35" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J35" s="3">
         <v>-300</v>
       </c>
       <c r="K35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
       <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>-100</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-15000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>40268</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>40178</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>40086</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,22 +2484,23 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
         <v>400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>600</v>
-      </c>
-      <c r="G41" s="3">
-        <v>100</v>
       </c>
       <c r="H41" s="3">
         <v>100</v>
@@ -2428,7 +2515,7 @@
         <v>100</v>
       </c>
       <c r="L41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41" s="3">
         <v>0</v>
@@ -2442,8 +2529,8 @@
       <c r="P41" s="3">
         <v>0</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
+      <c r="Q41" s="3">
+        <v>0</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>4</v>
@@ -2457,8 +2544,11 @@
       <c r="U41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,8 +2606,11 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2525,14 +2618,14 @@
         <v>700</v>
       </c>
       <c r="E43" s="3">
+        <v>700</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>200</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2548,8 +2641,8 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2575,8 +2668,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2590,7 +2686,7 @@
         <v>200</v>
       </c>
       <c r="G44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H44" s="3">
         <v>100</v>
@@ -2604,8 +2700,8 @@
       <c r="K44" s="3">
         <v>100</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
+      <c r="L44" s="3">
+        <v>100</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>4</v>
@@ -2619,8 +2715,8 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2634,8 +2730,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2657,8 +2756,8 @@
       <c r="I45" s="3">
         <v>0</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
+      <c r="J45" s="3">
+        <v>0</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
@@ -2669,8 +2768,8 @@
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
+      <c r="N45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
@@ -2693,22 +2792,25 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>900</v>
-      </c>
-      <c r="G46" s="3">
-        <v>200</v>
       </c>
       <c r="H46" s="3">
         <v>200</v>
@@ -2723,7 +2825,7 @@
         <v>200</v>
       </c>
       <c r="L46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
@@ -2737,8 +2839,8 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>4</v>
+      <c r="Q46" s="3">
+        <v>0</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>4</v>
@@ -2752,8 +2854,11 @@
       <c r="U46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2811,8 +2916,11 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2823,11 +2931,11 @@
         <v>100</v>
       </c>
       <c r="F48" s="3">
+        <v>100</v>
+      </c>
+      <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
       <c r="H48" s="3">
         <v>0</v>
       </c>
@@ -2835,19 +2943,19 @@
         <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
       </c>
       <c r="L48" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
+      <c r="N48" s="3">
+        <v>300</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
@@ -2864,25 +2972,28 @@
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="E49" s="3">
         <v>3900</v>
       </c>
       <c r="F49" s="3">
-        <v>4200</v>
+        <v>3900</v>
       </c>
       <c r="G49" s="3">
         <v>4200</v>
@@ -2899,8 +3010,8 @@
       <c r="K49" s="3">
         <v>4200</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
+      <c r="L49" s="3">
+        <v>4200</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>4</v>
@@ -2917,8 +3028,8 @@
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3164,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3067,8 +3187,8 @@
       <c r="H52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
@@ -3082,8 +3202,8 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
@@ -3100,14 +3220,17 @@
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,13 +3288,16 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="E54" s="3">
         <v>5300</v>
@@ -3180,7 +3306,7 @@
         <v>5300</v>
       </c>
       <c r="G54" s="3">
-        <v>4400</v>
+        <v>5300</v>
       </c>
       <c r="H54" s="3">
         <v>4400</v>
@@ -3192,16 +3318,16 @@
         <v>4400</v>
       </c>
       <c r="K54" s="3">
+        <v>4400</v>
+      </c>
+      <c r="L54" s="3">
         <v>4500</v>
-      </c>
-      <c r="L54" s="3">
-        <v>300</v>
       </c>
       <c r="M54" s="3">
         <v>300</v>
       </c>
       <c r="N54" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O54" s="3">
         <v>0</v>
@@ -3209,8 +3335,8 @@
       <c r="P54" s="3">
         <v>0</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>4</v>
+      <c r="Q54" s="3">
+        <v>0</v>
       </c>
       <c r="R54" s="3" t="s">
         <v>4</v>
@@ -3224,8 +3350,11 @@
       <c r="U54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,8 +3400,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3285,16 +3416,16 @@
         <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -3311,8 +3442,8 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
+      <c r="P57" s="3">
+        <v>0</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
@@ -3329,34 +3460,37 @@
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>200</v>
       </c>
       <c r="G58" s="3">
+        <v>200</v>
+      </c>
+      <c r="H58" s="3">
         <v>100</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
@@ -3364,14 +3498,14 @@
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="3">
-        <v>100</v>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
+      <c r="P58" s="3">
+        <v>100</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
@@ -3388,43 +3522,46 @@
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="E59" s="3">
         <v>1400</v>
       </c>
       <c r="F59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G59" s="3">
         <v>1500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>500</v>
-      </c>
-      <c r="L59" s="3">
-        <v>400</v>
       </c>
       <c r="M59" s="3">
         <v>400</v>
       </c>
       <c r="N59" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
@@ -3432,8 +3569,8 @@
       <c r="P59" s="3">
         <v>0</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
+      <c r="Q59" s="3">
+        <v>0</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>4</v>
@@ -3447,52 +3584,55 @@
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>500</v>
-      </c>
-      <c r="L60" s="3">
-        <v>400</v>
       </c>
       <c r="M60" s="3">
         <v>400</v>
       </c>
       <c r="N60" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="O60" s="3">
         <v>100</v>
       </c>
       <c r="P60" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>0</v>
       </c>
       <c r="R60" s="3" t="s">
         <v>4</v>
@@ -3506,8 +3646,11 @@
       <c r="U60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3565,8 +3708,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3574,13 +3720,13 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
+      <c r="G62" s="3">
+        <v>100</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>4</v>
@@ -3591,12 +3737,12 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3609,8 +3755,8 @@
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,52 +3956,55 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>600</v>
-      </c>
-      <c r="L66" s="3">
-        <v>400</v>
       </c>
       <c r="M66" s="3">
         <v>400</v>
       </c>
       <c r="N66" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="O66" s="3">
         <v>100</v>
       </c>
       <c r="P66" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>0</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>4</v>
@@ -3860,8 +4018,11 @@
       <c r="U66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,37 +4290,40 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-73900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-73000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-69500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-69100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-60100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-59700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-59400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-59100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-58800</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-56500</v>
       </c>
       <c r="M72" s="3">
         <v>-56500</v>
@@ -4158,13 +4332,13 @@
         <v>-56500</v>
       </c>
       <c r="O72" s="3">
-        <v>-56400</v>
+        <v>-56500</v>
       </c>
       <c r="P72" s="3">
         <v>-56400</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
+      <c r="Q72" s="3">
+        <v>-56400</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>4</v>
@@ -4178,8 +4352,11 @@
       <c r="U72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,37 +4538,40 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E76" s="3">
         <v>3800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3900</v>
-      </c>
-      <c r="L76" s="3">
-        <v>-100</v>
       </c>
       <c r="M76" s="3">
         <v>-100</v>
@@ -4397,10 +4583,10 @@
         <v>-100</v>
       </c>
       <c r="P76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>0</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>4</v>
@@ -4414,8 +4600,11 @@
       <c r="U76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>40268</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>40178</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>40086</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-400</v>
       </c>
       <c r="H81" s="3">
         <v>-400</v>
       </c>
       <c r="I81" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J81" s="3">
         <v>-300</v>
       </c>
       <c r="K81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
       <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>-100</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-15000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4817,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4628,11 +4827,11 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
@@ -4654,8 +4853,8 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>4</v>
@@ -4672,14 +4871,17 @@
       <c r="S83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,22 +5187,25 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-400</v>
       </c>
       <c r="F89" s="3">
         <v>-400</v>
       </c>
       <c r="G89" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="H89" s="3">
         <v>-200</v>
@@ -5000,11 +5217,11 @@
         <v>-200</v>
       </c>
       <c r="K89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
@@ -5020,8 +5237,8 @@
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>4</v>
@@ -5032,8 +5249,11 @@
       <c r="U89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,8 +5275,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5096,11 +5317,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -5114,8 +5335,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,46 +5459,49 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
@@ -5285,14 +5515,17 @@
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,25 +5793,28 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>600</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
-      </c>
-      <c r="H100" s="3">
-        <v>200</v>
       </c>
       <c r="I100" s="3">
         <v>200</v>
@@ -5577,19 +5823,19 @@
         <v>200</v>
       </c>
       <c r="K100" s="3">
+        <v>200</v>
+      </c>
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>4</v>
@@ -5609,8 +5855,11 @@
       <c r="U100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5668,23 +5917,26 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>500</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
@@ -5695,11 +5947,11 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
@@ -5715,8 +5967,8 @@
       <c r="Q102" s="3">
         <v>0</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>4</v>
@@ -5725,6 +5977,9 @@
         <v>4</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GEVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
   <si>
     <t>GEVI</t>
   </si>
@@ -656,127 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>40268</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>40178</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>40086</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
@@ -798,23 +802,26 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3">
         <v>1500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -828,10 +835,10 @@
         <v>100</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
@@ -842,17 +849,17 @@
       <c r="K9" s="3">
         <v>0</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M9" s="3">
-        <v>0</v>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N9" s="3">
         <v>0</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
+      <c r="O9" s="3">
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
@@ -863,82 +870,88 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T9" s="3">
         <v>1300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S10" s="3">
-        <v>200</v>
-      </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
-      <c r="U10" s="3">
-        <v>200</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,8 +974,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1023,8 +1037,11 @@
       <c r="V12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,20 +1102,23 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1108,17 +1128,17 @@
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1127,42 +1147,45 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3">
         <v>1800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>4000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>4</v>
+      <c r="E15" s="3">
+        <v>100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>100</v>
+      </c>
+      <c r="G15" s="3">
+        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1182,11 +1205,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1209,8 +1232,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,47 +1256,48 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1100</v>
       </c>
-      <c r="E17" s="3">
-        <v>4000</v>
-      </c>
       <c r="F17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G17" s="3">
         <v>600</v>
       </c>
-      <c r="G17" s="3">
-        <v>9200</v>
-      </c>
       <c r="H17" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I17" s="3">
         <v>400</v>
       </c>
-      <c r="I17" s="3">
-        <v>500</v>
-      </c>
       <c r="J17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K17" s="3">
         <v>300</v>
       </c>
       <c r="L17" s="3">
+        <v>300</v>
+      </c>
+      <c r="M17" s="3">
         <v>2400</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
       <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
         <v>100</v>
       </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
       <c r="P17" s="3">
         <v>0</v>
       </c>
@@ -1278,84 +1305,90 @@
         <v>0</v>
       </c>
       <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
         <v>100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-900</v>
       </c>
-      <c r="E18" s="3">
-        <v>-3600</v>
-      </c>
       <c r="F18" s="3">
-        <v>-300</v>
+        <v>-2600</v>
       </c>
       <c r="G18" s="3">
-        <v>-9000</v>
+        <v>-400</v>
       </c>
       <c r="H18" s="3">
-        <v>-400</v>
+        <v>-9100</v>
       </c>
       <c r="I18" s="3">
         <v>-400</v>
       </c>
       <c r="J18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="K18" s="3">
         <v>-300</v>
       </c>
       <c r="L18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M18" s="3">
         <v>-2400</v>
       </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
       <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
       <c r="P18" s="3">
         <v>0</v>
       </c>
       <c r="Q18" s="3">
         <v>0</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>-4200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,31 +1411,32 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1425,93 +1459,99 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>1700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-800</v>
       </c>
-      <c r="E21" s="3">
-        <v>-3500</v>
-      </c>
       <c r="F21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="G21" s="3">
         <v>-100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-400</v>
       </c>
       <c r="I21" s="3">
         <v>-400</v>
       </c>
       <c r="J21" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="K21" s="3">
         <v>-300</v>
       </c>
       <c r="L21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M21" s="3">
         <v>-2300</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
         <v>0</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3">
-        <v>0</v>
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q21" s="3">
         <v>0</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-2100</v>
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T21" s="3">
         <v>-2100</v>
       </c>
       <c r="U21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="V21" s="3">
         <v>-1400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1549,56 +1589,59 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T22" s="3">
         <v>900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-400</v>
       </c>
-      <c r="G23" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H23" s="3">
-        <v>-400</v>
+        <v>-9100</v>
       </c>
       <c r="I23" s="3">
         <v>-400</v>
       </c>
       <c r="J23" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="K23" s="3">
         <v>-300</v>
       </c>
       <c r="L23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M23" s="3">
         <v>-2300</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
       <c r="N23" s="3">
         <v>0</v>
       </c>
@@ -1612,45 +1655,48 @@
         <v>0</v>
       </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1673,23 +1719,26 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,41 +1799,44 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-400</v>
       </c>
-      <c r="G26" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H26" s="3">
-        <v>-400</v>
+        <v>-9100</v>
       </c>
       <c r="I26" s="3">
         <v>-400</v>
       </c>
       <c r="J26" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="K26" s="3">
         <v>-300</v>
       </c>
       <c r="L26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
       <c r="N26" s="3">
         <v>0</v>
       </c>
@@ -1798,55 +1850,58 @@
         <v>0</v>
       </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-400</v>
       </c>
-      <c r="G27" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H27" s="3">
-        <v>-400</v>
+        <v>-9100</v>
       </c>
       <c r="I27" s="3">
         <v>-400</v>
       </c>
       <c r="J27" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="K27" s="3">
         <v>-300</v>
       </c>
       <c r="L27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
       <c r="N27" s="3">
         <v>0</v>
       </c>
@@ -1860,22 +1915,25 @@
         <v>0</v>
       </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,16 +1994,19 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>4</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1972,34 +2033,37 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-100</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-100</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T29" s="3">
         <v>8300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-7400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,31 +2189,34 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2169,85 +2239,91 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-400</v>
       </c>
-      <c r="G33" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H33" s="3">
-        <v>-400</v>
+        <v>-9100</v>
       </c>
       <c r="I33" s="3">
         <v>-400</v>
       </c>
       <c r="J33" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="K33" s="3">
         <v>-300</v>
       </c>
       <c r="L33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
       <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
       <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-15000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2384,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-400</v>
       </c>
-      <c r="G35" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H35" s="3">
-        <v>-400</v>
+        <v>-9100</v>
       </c>
       <c r="I35" s="3">
         <v>-400</v>
       </c>
       <c r="J35" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="K35" s="3">
         <v>-300</v>
       </c>
       <c r="L35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
       <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
       <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-15000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>40268</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>40178</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>40086</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,25 +2571,26 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
         <v>500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>600</v>
-      </c>
-      <c r="H41" s="3">
-        <v>100</v>
       </c>
       <c r="I41" s="3">
         <v>100</v>
@@ -2518,7 +2605,7 @@
         <v>100</v>
       </c>
       <c r="M41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41" s="3">
         <v>0</v>
@@ -2532,8 +2619,8 @@
       <c r="Q41" s="3">
         <v>0</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>4</v>
+      <c r="R41" s="3">
+        <v>0</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>4</v>
@@ -2547,8 +2634,11 @@
       <c r="V41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2609,26 +2699,29 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="E43" s="3">
         <v>700</v>
       </c>
       <c r="F43" s="3">
+        <v>700</v>
+      </c>
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2644,8 +2737,8 @@
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2671,13 +2764,16 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E44" s="3">
         <v>200</v>
@@ -2689,7 +2785,7 @@
         <v>200</v>
       </c>
       <c r="H44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I44" s="3">
         <v>100</v>
@@ -2703,8 +2799,8 @@
       <c r="L44" s="3">
         <v>100</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
+      <c r="M44" s="3">
+        <v>100</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>4</v>
@@ -2718,8 +2814,8 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -2733,34 +2829,37 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>4</v>
@@ -2771,8 +2870,8 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -2795,25 +2894,28 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>900</v>
-      </c>
-      <c r="H46" s="3">
-        <v>200</v>
       </c>
       <c r="I46" s="3">
         <v>200</v>
@@ -2828,7 +2930,7 @@
         <v>200</v>
       </c>
       <c r="M46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N46" s="3">
         <v>0</v>
@@ -2842,8 +2944,8 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>4</v>
+      <c r="R46" s="3">
+        <v>0</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>4</v>
@@ -2857,31 +2959,34 @@
       <c r="V46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2919,8 +3024,11 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2934,11 +3042,11 @@
         <v>100</v>
       </c>
       <c r="G48" s="3">
+        <v>100</v>
+      </c>
+      <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
       <c r="I48" s="3">
         <v>0</v>
       </c>
@@ -2946,19 +3054,19 @@
         <v>0</v>
       </c>
       <c r="K48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3">
         <v>100</v>
       </c>
       <c r="M48" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N48" s="3">
         <v>300</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
+      <c r="O48" s="3">
+        <v>300</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
@@ -2975,14 +3083,17 @@
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2990,13 +3101,13 @@
         <v>3800</v>
       </c>
       <c r="E49" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="F49" s="3">
         <v>3900</v>
       </c>
       <c r="G49" s="3">
-        <v>4200</v>
+        <v>3900</v>
       </c>
       <c r="H49" s="3">
         <v>4200</v>
@@ -3013,8 +3124,8 @@
       <c r="L49" s="3">
         <v>4200</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>4</v>
+      <c r="M49" s="3">
+        <v>4200</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>4</v>
@@ -3031,8 +3142,8 @@
       <c r="R49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3043,8 +3154,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,8 +3284,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3190,8 +3310,8 @@
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3205,8 +3325,8 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
@@ -3223,14 +3343,17 @@
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,16 +3414,19 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E54" s="3">
         <v>5400</v>
-      </c>
-      <c r="E54" s="3">
-        <v>5300</v>
       </c>
       <c r="F54" s="3">
         <v>5300</v>
@@ -3309,7 +3435,7 @@
         <v>5300</v>
       </c>
       <c r="H54" s="3">
-        <v>4400</v>
+        <v>5300</v>
       </c>
       <c r="I54" s="3">
         <v>4400</v>
@@ -3321,16 +3447,16 @@
         <v>4400</v>
       </c>
       <c r="L54" s="3">
+        <v>4400</v>
+      </c>
+      <c r="M54" s="3">
         <v>4500</v>
-      </c>
-      <c r="M54" s="3">
-        <v>300</v>
       </c>
       <c r="N54" s="3">
         <v>300</v>
       </c>
       <c r="O54" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P54" s="3">
         <v>0</v>
@@ -3338,8 +3464,8 @@
       <c r="Q54" s="3">
         <v>0</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>4</v>
+      <c r="R54" s="3">
+        <v>0</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>4</v>
@@ -3353,8 +3479,11 @@
       <c r="V54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,13 +3531,14 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
@@ -3419,16 +3550,16 @@
         <v>100</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J57" s="3">
         <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -3445,8 +3576,8 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
+      <c r="Q57" s="3">
+        <v>0</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>4</v>
@@ -3463,37 +3594,40 @@
       <c r="V57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>700</v>
+        <v>2000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F58" s="3">
-        <v>200</v>
+        <v>1400</v>
       </c>
       <c r="G58" s="3">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="H58" s="3">
-        <v>100</v>
+        <v>1700</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
@@ -3501,14 +3635,14 @@
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O58" s="3">
-        <v>100</v>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
+      <c r="Q58" s="3">
+        <v>100</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
@@ -3525,46 +3659,49 @@
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>500</v>
-      </c>
-      <c r="M59" s="3">
-        <v>400</v>
       </c>
       <c r="N59" s="3">
         <v>400</v>
       </c>
       <c r="O59" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -3572,8 +3709,8 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
+      <c r="R59" s="3">
+        <v>0</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
@@ -3587,8 +3724,11 @@
       <c r="V59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3596,46 +3736,46 @@
         <v>2100</v>
       </c>
       <c r="E60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F60" s="3">
         <v>1500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>500</v>
-      </c>
-      <c r="M60" s="3">
-        <v>400</v>
       </c>
       <c r="N60" s="3">
         <v>400</v>
       </c>
       <c r="O60" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="P60" s="3">
         <v>100</v>
       </c>
       <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>4</v>
@@ -3649,8 +3789,11 @@
       <c r="V60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3664,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -3711,41 +3854,44 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="G62" s="3">
-        <v>100</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L62" s="3">
-        <v>100</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3758,8 +3904,8 @@
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
@@ -3773,8 +3919,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,8 +4114,11 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3968,46 +4126,46 @@
         <v>2100</v>
       </c>
       <c r="E66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F66" s="3">
         <v>1500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>600</v>
-      </c>
-      <c r="M66" s="3">
-        <v>400</v>
       </c>
       <c r="N66" s="3">
         <v>400</v>
       </c>
       <c r="O66" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="P66" s="3">
         <v>100</v>
       </c>
       <c r="Q66" s="3">
-        <v>0</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="R66" s="3">
+        <v>0</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>4</v>
@@ -4021,8 +4179,11 @@
       <c r="V66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,40 +4464,43 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-74600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-73900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-73000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-69500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-69100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-60100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-59700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-59400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-59100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-58800</v>
-      </c>
-      <c r="M72" s="3">
-        <v>-56500</v>
       </c>
       <c r="N72" s="3">
         <v>-56500</v>
@@ -4335,13 +4509,13 @@
         <v>-56500</v>
       </c>
       <c r="P72" s="3">
-        <v>-56400</v>
+        <v>-56500</v>
       </c>
       <c r="Q72" s="3">
         <v>-56400</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
+      <c r="R72" s="3">
+        <v>-56400</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>4</v>
@@ -4355,8 +4529,11 @@
       <c r="V72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,40 +4724,43 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E76" s="3">
         <v>3200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3900</v>
-      </c>
-      <c r="M76" s="3">
-        <v>-100</v>
       </c>
       <c r="N76" s="3">
         <v>-100</v>
@@ -4586,10 +4772,10 @@
         <v>-100</v>
       </c>
       <c r="Q76" s="3">
-        <v>0</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="R76" s="3">
+        <v>0</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>4</v>
@@ -4603,8 +4789,11 @@
       <c r="V76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4854,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>40268</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>40178</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>40086</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-400</v>
       </c>
-      <c r="G81" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H81" s="3">
-        <v>-400</v>
+        <v>-9100</v>
       </c>
       <c r="I81" s="3">
         <v>-400</v>
       </c>
       <c r="J81" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="K81" s="3">
         <v>-300</v>
       </c>
       <c r="L81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
       <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
       <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-15000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,19 +5016,20 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
@@ -4841,8 +5040,8 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -4856,8 +5055,8 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>4</v>
@@ -4874,14 +5073,17 @@
       <c r="T83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,25 +5404,28 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-300</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-400</v>
       </c>
       <c r="G89" s="3">
         <v>-400</v>
       </c>
       <c r="H89" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="I89" s="3">
         <v>-200</v>
@@ -5220,11 +5437,11 @@
         <v>-200</v>
       </c>
       <c r="L89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
         <v>0</v>
       </c>
@@ -5240,8 +5457,8 @@
       <c r="R89" s="3">
         <v>0</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>4</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>4</v>
@@ -5252,8 +5469,11 @@
       <c r="V89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,19 +5496,20 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -5296,11 +5517,11 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5320,11 +5541,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -5338,8 +5559,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,8 +5689,11 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5473,38 +5703,38 @@
       <c r="E94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>4</v>
@@ -5518,14 +5748,17 @@
       <c r="T94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,31 +5781,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,28 +6039,31 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
-      </c>
-      <c r="I100" s="3">
-        <v>200</v>
       </c>
       <c r="J100" s="3">
         <v>200</v>
@@ -5826,19 +6072,19 @@
         <v>200</v>
       </c>
       <c r="L100" s="3">
+        <v>200</v>
+      </c>
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>4</v>
@@ -5858,31 +6104,34 @@
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5920,26 +6169,29 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>500</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
@@ -5950,11 +6202,11 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
@@ -5970,8 +6222,8 @@
       <c r="R102" s="3">
         <v>0</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>4</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>4</v>
@@ -5980,6 +6232,9 @@
         <v>4</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GEVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
   <si>
     <t>GEVI</t>
   </si>
@@ -656,137 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>40268</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>40178</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>40086</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
@@ -805,31 +812,37 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>4</v>
+      <c r="S8" s="3">
+        <v>0</v>
       </c>
       <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3">
         <v>1500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>4000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F9" s="3">
         <v>100</v>
@@ -841,10 +854,10 @@
         <v>100</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -852,20 +865,20 @@
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
+      <c r="M9" s="3">
+        <v>0</v>
       </c>
       <c r="N9" s="3">
         <v>0</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>4</v>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>4</v>
@@ -873,64 +886,70 @@
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V9" s="3">
         <v>1300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>3800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="F10" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
       </c>
       <c r="H10" s="3">
+        <v>300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>200</v>
+      </c>
+      <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
       <c r="K10" s="3">
         <v>0</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10" s="3">
         <v>0</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
@@ -938,20 +957,26 @@
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T10" s="3">
-        <v>200</v>
-      </c>
-      <c r="U10" s="3">
-        <v>0</v>
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V10" s="3">
         <v>200</v>
       </c>
       <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y10" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,16 +1000,18 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>4</v>
+      <c r="E12" s="3">
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>4</v>
@@ -1040,8 +1067,14 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,73 +1138,85 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="3">
         <v>1800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>4000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>1900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1185,7 +1230,7 @@
         <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1194,10 +1239,10 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1208,14 +1253,14 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1235,8 +1280,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1308,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F17" s="3">
         <v>700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>600</v>
-      </c>
-      <c r="H17" s="3">
-        <v>9300</v>
       </c>
       <c r="I17" s="3">
         <v>400</v>
       </c>
       <c r="J17" s="3">
+        <v>9300</v>
+      </c>
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
+        <v>400</v>
+      </c>
+      <c r="M17" s="3">
         <v>300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2400</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
         <v>100</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
       <c r="R17" s="3">
         <v>0</v>
       </c>
       <c r="S17" s="3">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>5700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>6100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>8000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2400</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
         <v>0</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
+      <c r="S18" s="3">
+        <v>0</v>
       </c>
       <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3">
         <v>-4200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-5200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-4000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,16 +1477,18 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>400</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>4</v>
@@ -1438,11 +1505,11 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1462,102 +1529,114 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
         <v>1700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>2900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>2800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-2600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-9000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2300</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
+      <c r="P21" s="3">
+        <v>0</v>
       </c>
       <c r="Q21" s="3">
         <v>0</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
+        <v>0</v>
       </c>
       <c r="T21" s="3">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>-2100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-2100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-1400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>200</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1592,62 +1671,68 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V22" s="3">
         <v>900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>5300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>1800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="H23" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2300</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
       <c r="P23" s="3">
         <v>0</v>
       </c>
@@ -1658,22 +1743,28 @@
         <v>0</v>
       </c>
       <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-3400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-7600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-3100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1698,11 +1789,11 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1722,23 +1813,29 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>4</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,47 +1899,53 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="H26" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="L26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
         <v>0</v>
       </c>
@@ -1853,61 +1956,67 @@
         <v>0</v>
       </c>
       <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-3800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-7600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-3100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="H27" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
       </c>
-      <c r="J27" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
         <v>0</v>
       </c>
@@ -1918,22 +2027,28 @@
         <v>0</v>
       </c>
       <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-3800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-7600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-3100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2112,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2036,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2047,23 +2168,29 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>4</v>
+      <c r="S29" s="3">
+        <v>-100</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V29" s="3">
         <v>8300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>-7400</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>-100</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2254,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,16 +2325,22 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-400</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>4</v>
@@ -2218,11 +2357,11 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2242,61 +2381,67 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-2900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-2800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="H33" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
       </c>
-      <c r="J33" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
-      </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-100</v>
       </c>
       <c r="P33" s="3">
         <v>0</v>
@@ -2311,19 +2456,25 @@
         <v>-100</v>
       </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V33" s="3">
         <v>4500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-15000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-3200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,46 +2538,52 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="H35" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
       </c>
-      <c r="J35" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
-      </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-100</v>
       </c>
       <c r="P35" s="3">
         <v>0</v>
@@ -2441,89 +2598,101 @@
         <v>-100</v>
       </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V35" s="3">
         <v>4500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-15000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-3200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>40268</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>40178</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>40086</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2716,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,31 +2743,33 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>800</v>
+      </c>
+      <c r="F41" s="3">
         <v>300</v>
-      </c>
-      <c r="E41" s="3">
-        <v>500</v>
-      </c>
-      <c r="F41" s="3">
-        <v>400</v>
       </c>
       <c r="G41" s="3">
         <v>500</v>
       </c>
       <c r="H41" s="3">
+        <v>400</v>
+      </c>
+      <c r="I41" s="3">
+        <v>500</v>
+      </c>
+      <c r="J41" s="3">
         <v>600</v>
-      </c>
-      <c r="I41" s="3">
-        <v>100</v>
-      </c>
-      <c r="J41" s="3">
-        <v>100</v>
       </c>
       <c r="K41" s="3">
         <v>100</v>
@@ -2608,10 +2781,10 @@
         <v>100</v>
       </c>
       <c r="N41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P41" s="3">
         <v>0</v>
@@ -2622,11 +2795,11 @@
       <c r="R41" s="3">
         <v>0</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>4</v>
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3">
+        <v>0</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>4</v>
@@ -2637,8 +2810,14 @@
       <c r="W41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,32 +2881,38 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>300</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2740,11 +2925,11 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2767,8 +2952,14 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2776,10 +2967,10 @@
         <v>300</v>
       </c>
       <c r="E44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F44" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G44" s="3">
         <v>200</v>
@@ -2788,10 +2979,10 @@
         <v>200</v>
       </c>
       <c r="I44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K44" s="3">
         <v>100</v>
@@ -2802,11 +2993,11 @@
       <c r="M44" s="3">
         <v>100</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
+      <c r="N44" s="3">
+        <v>100</v>
+      </c>
+      <c r="O44" s="3">
+        <v>100</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
@@ -2817,11 +3008,11 @@
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
-      </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
@@ -2832,8 +3023,14 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2841,13 +3038,13 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
@@ -2858,14 +3055,14 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
+      <c r="M45" s="3">
+        <v>0</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>4</v>
@@ -2873,11 +3070,11 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -2897,31 +3094,37 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F46" s="3">
         <v>1100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>900</v>
-      </c>
-      <c r="I46" s="3">
-        <v>200</v>
-      </c>
-      <c r="J46" s="3">
-        <v>200</v>
       </c>
       <c r="K46" s="3">
         <v>200</v>
@@ -2933,10 +3136,10 @@
         <v>200</v>
       </c>
       <c r="N46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P46" s="3">
         <v>0</v>
@@ -2947,11 +3150,11 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>4</v>
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3">
+        <v>0</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>4</v>
@@ -2962,8 +3165,14 @@
       <c r="W46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2988,11 +3197,11 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3027,16 +3236,22 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F48" s="3">
         <v>100</v>
@@ -3045,35 +3260,35 @@
         <v>100</v>
       </c>
       <c r="H48" s="3">
+        <v>100</v>
+      </c>
+      <c r="I48" s="3">
+        <v>100</v>
+      </c>
+      <c r="J48" s="3">
         <v>200</v>
       </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
       <c r="K48" s="3">
         <v>0</v>
       </c>
       <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3">
         <v>100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3086,34 +3301,40 @@
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F49" s="3">
         <v>3800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3900</v>
-      </c>
-      <c r="H49" s="3">
-        <v>4200</v>
-      </c>
-      <c r="I49" s="3">
-        <v>4200</v>
       </c>
       <c r="J49" s="3">
         <v>4200</v>
@@ -3127,11 +3348,11 @@
       <c r="M49" s="3">
         <v>4200</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
+      <c r="N49" s="3">
+        <v>4200</v>
+      </c>
+      <c r="O49" s="3">
+        <v>4200</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
@@ -3145,11 +3366,11 @@
       <c r="S49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
-      </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3157,8 +3378,14 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3449,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,13 +3520,19 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>0</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>4</v>
@@ -3313,11 +3552,11 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -3328,11 +3567,11 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>4</v>
@@ -3346,14 +3585,20 @@
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,31 +3662,37 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F54" s="3">
         <v>4900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5400</v>
-      </c>
-      <c r="F54" s="3">
-        <v>5300</v>
-      </c>
-      <c r="G54" s="3">
-        <v>5300</v>
       </c>
       <c r="H54" s="3">
         <v>5300</v>
       </c>
       <c r="I54" s="3">
-        <v>4400</v>
+        <v>5300</v>
       </c>
       <c r="J54" s="3">
-        <v>4400</v>
+        <v>5300</v>
       </c>
       <c r="K54" s="3">
         <v>4400</v>
@@ -3450,28 +3701,28 @@
         <v>4400</v>
       </c>
       <c r="M54" s="3">
+        <v>4400</v>
+      </c>
+      <c r="N54" s="3">
+        <v>4400</v>
+      </c>
+      <c r="O54" s="3">
         <v>4500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>300</v>
       </c>
-      <c r="P54" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>0</v>
-      </c>
       <c r="R54" s="3">
         <v>0</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>4</v>
+      <c r="S54" s="3">
+        <v>0</v>
+      </c>
+      <c r="T54" s="3">
+        <v>0</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>4</v>
@@ -3482,8 +3733,14 @@
       <c r="W54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3764,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,19 +3791,21 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
-        <v>100</v>
-      </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G57" s="3">
         <v>100</v>
@@ -3553,19 +3814,19 @@
         <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>100</v>
       </c>
       <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -3579,11 +3840,11 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>4</v>
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>4</v>
@@ -3597,59 +3858,65 @@
       <c r="W57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>900</v>
+      </c>
+      <c r="F58" s="3">
         <v>2000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1400</v>
       </c>
-      <c r="G58" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>300</v>
+      </c>
+      <c r="J58" s="3">
         <v>1700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3662,16 +3929,22 @@
       <c r="W58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
+      <c r="D59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1100</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>4</v>
@@ -3682,41 +3955,41 @@
       <c r="H59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
+      <c r="I59" s="3">
+        <v>1300</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>400</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
       <c r="R59" s="3">
         <v>0</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3">
+        <v>0</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>4</v>
@@ -3727,61 +4000,67 @@
       <c r="W59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F60" s="3">
         <v>2100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>4</v>
+      <c r="T60" s="3">
+        <v>0</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>4</v>
@@ -3792,8 +4071,14 @@
       <c r="W60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3807,17 +4092,17 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3857,8 +4142,14 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3889,15 +4180,15 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3907,11 +4198,11 @@
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -3922,8 +4213,14 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4284,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4355,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,61 +4426,67 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F66" s="3">
         <v>2100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>100</v>
       </c>
-      <c r="R66" s="3">
-        <v>0</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>4</v>
+      <c r="T66" s="3">
+        <v>0</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>4</v>
@@ -4182,8 +4497,14 @@
       <c r="W66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4528,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4595,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4666,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4737,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,62 +4808,68 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-87300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-76400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-74600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-73900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-73000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-69500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-69100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-60100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-59700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-59400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-59100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-58800</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-56500</v>
-      </c>
-      <c r="O72" s="3">
-        <v>-56500</v>
       </c>
       <c r="P72" s="3">
         <v>-56500</v>
       </c>
       <c r="Q72" s="3">
+        <v>-56500</v>
+      </c>
+      <c r="R72" s="3">
+        <v>-56500</v>
+      </c>
+      <c r="S72" s="3">
         <v>-56400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-56400</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4532,8 +4879,14 @@
       <c r="W72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4950,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +5021,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,46 +5092,52 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F76" s="3">
         <v>2800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>3600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3900</v>
-      </c>
-      <c r="N76" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O76" s="3">
-        <v>-100</v>
       </c>
       <c r="P76" s="3">
         <v>-100</v>
@@ -4775,13 +5146,13 @@
         <v>-100</v>
       </c>
       <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="S76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>4</v>
@@ -4792,8 +5163,14 @@
       <c r="W76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,116 +5234,128 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>40268</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>40178</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>40086</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>39994</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="H81" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
       </c>
-      <c r="J81" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
-      </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-100</v>
       </c>
       <c r="P81" s="3">
         <v>0</v>
@@ -4981,19 +5370,25 @@
         <v>-100</v>
       </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V81" s="3">
         <v>4500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-15000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-3200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-9400</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5412,10 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5040,14 +5437,14 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -5058,11 +5455,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>4</v>
@@ -5076,14 +5473,20 @@
       <c r="U83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5550,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5621,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5692,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5763,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,31 +5834,37 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
-        <v>-400</v>
-      </c>
       <c r="F89" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="G89" s="3">
         <v>-400</v>
       </c>
       <c r="H89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3">
-        <v>-200</v>
-      </c>
       <c r="J89" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="K89" s="3">
         <v>-200</v>
@@ -5440,14 +5873,14 @@
         <v>-200</v>
       </c>
       <c r="M89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
         <v>0</v>
       </c>
@@ -5460,11 +5893,11 @@
       <c r="S89" s="3">
         <v>0</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>4</v>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>4</v>
@@ -5472,8 +5905,14 @@
       <c r="W89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,13 +5936,15 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>4</v>
+      <c r="D91" s="3">
+        <v>0</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>4</v>
@@ -5511,23 +5952,23 @@
       <c r="F91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5544,14 +5985,14 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -5562,8 +6003,14 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +6074,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,13 +6145,19 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>0</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>4</v>
@@ -5706,41 +6165,41 @@
       <c r="F94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
@@ -5751,14 +6210,20 @@
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6247,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5808,11 +6275,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5847,8 +6314,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6385,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6456,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,55 +6527,61 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
-      </c>
-      <c r="J100" s="3">
-        <v>200</v>
-      </c>
-      <c r="K100" s="3">
-        <v>200</v>
       </c>
       <c r="L100" s="3">
         <v>200</v>
       </c>
       <c r="M100" s="3">
+        <v>200</v>
+      </c>
+      <c r="N100" s="3">
+        <v>200</v>
+      </c>
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>4</v>
@@ -6107,8 +6598,14 @@
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6133,11 +6630,11 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6172,32 +6669,38 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-200</v>
+        <v>3000</v>
       </c>
       <c r="E102" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F102" s="3">
         <v>-200</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>500</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
@@ -6205,14 +6708,14 @@
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
@@ -6225,16 +6728,22 @@
       <c r="S102" s="3">
         <v>0</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>4</v>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
